--- a/Result/profitability/4541.xlsx
+++ b/Result/profitability/4541.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7669,6 +7669,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>549</v>
+      </c>
+      <c r="D58" t="n">
+        <v>401</v>
+      </c>
+      <c r="E58" t="n">
+        <v>148</v>
+      </c>
+      <c r="F58" t="n">
+        <v>26.99</v>
+      </c>
+      <c r="G58" t="n">
+        <v>108</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>19.61%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>99</v>
+      </c>
+      <c r="K58" t="n">
+        <v>86</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="N58" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X58" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>6.469999999999999</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.3153021442495125</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-3.24561403508772</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>2.299999999999997</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0.09315512353179423</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
